--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA219"/>
+  <dimension ref="A1:AA220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22320,6 +22320,91 @@
       <c r="Z219" s="2" t="inlineStr"/>
       <c r="AA219" s="2" t="inlineStr"/>
     </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>158732</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg, Kalininskiy</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>84a Polyustrovsky Prospekt, Evropolis Shopping Center</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>194100</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>office@wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>35510140</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr"/>
+      <c r="S220" s="2" t="inlineStr"/>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr"/>
+      <c r="X220" s="2" t="inlineStr"/>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA220"/>
+  <dimension ref="A1:AA221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22405,6 +22405,91 @@
       <c r="Z220" s="2" t="inlineStr"/>
       <c r="AA220" s="2" t="inlineStr"/>
     </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>158732</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg, Kalininskiy</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>84a Polyustrovsky Prospekt, Evropolis Shopping Center</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>194100</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>office@wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr"/>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>35510140</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr"/>
+      <c r="S221" s="2" t="inlineStr"/>
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr"/>
+      <c r="X221" s="2" t="inlineStr"/>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA221"/>
+  <dimension ref="A1:AA222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22490,6 +22490,91 @@
       <c r="Z221" s="2" t="inlineStr"/>
       <c r="AA221" s="2" t="inlineStr"/>
     </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>158732</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg, Kalininskiy</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>84a Polyustrovsky Prospekt, Evropolis Shopping Center</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>194100</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>office@wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr"/>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>35510140</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr"/>
+      <c r="S222" s="2" t="inlineStr"/>
+      <c r="T222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr"/>
+      <c r="X222" s="2" t="inlineStr"/>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA222"/>
+  <dimension ref="A1:AA223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22575,6 +22575,91 @@
       <c r="Z222" s="2" t="inlineStr"/>
       <c r="AA222" s="2" t="inlineStr"/>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Apellason, Ooo</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>158732</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg, Kalininskiy</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>84a Polyustrovsky Prospekt, Evropolis Shopping Center</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>194100</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>office@wineassemblage.ru</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr"/>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>35510140</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr"/>
+      <c r="S223" s="2" t="inlineStr"/>
+      <c r="T223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr"/>
+      <c r="X223" s="2" t="inlineStr"/>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA223"/>
+  <dimension ref="A1:AA224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22660,6 +22660,111 @@
       <c r="Z223" s="2" t="inlineStr"/>
       <c r="AA223" s="2" t="inlineStr"/>
     </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Grape Wines</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Grape Wines</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>23068</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Sokol'niki</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>11 Ulitsa Lobachika</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>107113</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://grapewines.ru, https://grapewinestore.ru</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>info@grapewines.ru</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>+7 499 702-39-71</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>47394532</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr"/>
+      <c r="S224" s="2" t="inlineStr"/>
+      <c r="T224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapewines_ru/</t>
+        </is>
+      </c>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdUfknf_Pa-XaCy1EgyH19g</t>
+        </is>
+      </c>
+      <c r="W224" s="2" t="inlineStr">
+        <is>
+          <t>Evgeny Melnikov</t>
+        </is>
+      </c>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evgeny-melnikov-599ba975/?originalSubdomain=ru</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA224"/>
+  <dimension ref="A1:AA227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22765,6 +22765,253 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIZH GRUPP, OOO</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>167907</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Kostroma</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr"/>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>d. 11 str. 3 pom. 19 ETAZH 3, ul. Zelenaya</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>156019</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>https://vinsklad.ru</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>13798642</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>info@vinsklad.ru</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>+7 494 462-43-41</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>92984429</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr"/>
+      <c r="S225" s="2" t="inlineStr"/>
+      <c r="T225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr"/>
+      <c r="X225" s="2" t="inlineStr"/>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>TK KLEVER, OOO</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr"/>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>167906</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Feodosiya</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>ul. Desantnikov 7</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>298100</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://tc-clover.ru</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>45547787</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>info.klever@yandex.ru</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>00705887</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr"/>
+      <c r="S226" s="2" t="inlineStr"/>
+      <c r="T226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/clover_tc/</t>
+        </is>
+      </c>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr"/>
+      <c r="X226" s="2" t="inlineStr"/>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>AST-International Environment LLC</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Ast Wine</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>167835</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>st. Kakhovka, 23</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>https://ast.wine</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>info@ast.wine</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 993-99-99</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>29395479</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr"/>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61560463749280#</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ast.wine.shop/</t>
+        </is>
+      </c>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr"/>
+      <c r="X227" s="2" t="inlineStr"/>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA227"/>
+  <dimension ref="A1:AA252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23012,6 +23012,2211 @@
       <c r="Z227" s="2" t="inlineStr"/>
       <c r="AA227" s="2" t="inlineStr"/>
     </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>LEGENDA VINODELIYA, OOO</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr"/>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>167971</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>d. 29 etazh 1 pom. I kom. 5, prospekt Michurinski</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>119607</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://dream-wine.ru</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>4292686</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>web@dream-wine.ru</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 956-55-42</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>16180122</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr"/>
+      <c r="S228" s="2" t="inlineStr"/>
+      <c r="T228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr">
+        <is>
+          <t>Aleksei Valerevich Papin</t>
+        </is>
+      </c>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>VINOTERAPIYA, OOO</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr"/>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>167970</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>St. Petersburg</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>d. 16 litera A pom. 23, ul. Chapaeva</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>197101</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>https://pianobutik.ru</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>2464360</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>vino@pianobutik.ru</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>+7 812 983-27-00</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>32816192</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr"/>
+      <c r="S229" s="2" t="inlineStr"/>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pianopiano_butik/</t>
+        </is>
+      </c>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr">
+        <is>
+          <t>Aleksei Pavlovich Chizhov</t>
+        </is>
+      </c>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>PRODSNAB, OOO</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr"/>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>167968</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Kostroma</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>d. 221 kv. 24, ul. Shagova</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>156008</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://dutyfree-online.ru</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>2844739</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>sale@dutyfree-online.ru</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr"/>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>85888435</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr"/>
+      <c r="S230" s="2" t="inlineStr"/>
+      <c r="T230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr">
+        <is>
+          <t>Elena Vladimirovna Krovatkina</t>
+        </is>
+      </c>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>VAIN MARKET, OOO</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr"/>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>167967</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>d. 2 str. 1 pom. 1/1, ul. Usacheva</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>119048</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>https://salon-usacheva.ru</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>303293</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>vinemarket@mail.ru</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 723-52-52</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>95767661</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr"/>
+      <c r="S231" s="2" t="inlineStr"/>
+      <c r="T231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr">
+        <is>
+          <t>Ruslan Andreevich Iskandarov</t>
+        </is>
+      </c>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Negowine, Ooo</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr"/>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>167962</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Kazan</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>d. 25 pom. 15, ul. Zhukovskogo</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>420015</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>https://gal-vin.ru</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>333194</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>jukovskogo@gal-vin.ru</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>+7 843 236-00-80</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>59309141</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr"/>
+      <c r="S232" s="2" t="inlineStr"/>
+      <c r="T232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr">
+        <is>
+          <t>Marina Mikhailovna Zaipina</t>
+        </is>
+      </c>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>BTV, OOO</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Elite Wine</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>167960</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Tambov</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>d. 211V pom. 4, ul. Michurinskaya</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>392027</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>https://elitewine.ru</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>191788</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>admin@elitewine.ru</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr"/>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>53361471</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr"/>
+      <c r="S233" s="2" t="inlineStr"/>
+      <c r="T233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr"/>
+      <c r="W233" s="2" t="inlineStr">
+        <is>
+          <t>Tatyana Vladimirovna Belousova</t>
+        </is>
+      </c>
+      <c r="X233" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y233" s="2" t="inlineStr"/>
+      <c r="Z233" s="2" t="inlineStr"/>
+      <c r="AA233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>GETNATUN, OOO</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr"/>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>167958</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>d. 6 etazh 1 kom. 20 20A 20B 20V, per. Bolshoi Kislovski</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>125009</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>https://getnatoun.ru</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>184941</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>getnatoun@bk.ru</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 933-71-27</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>15135059</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr"/>
+      <c r="S234" s="2" t="inlineStr"/>
+      <c r="T234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr">
+        <is>
+          <t>Arevik Robertovna Artashyan</t>
+        </is>
+      </c>
+      <c r="X234" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y234" s="2" t="inlineStr"/>
+      <c r="Z234" s="2" t="inlineStr"/>
+      <c r="AA234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>VINOMANIYA, OOO</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr"/>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>167957</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Lipetsk</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>d. 10 kv. 36A, ul. Belyanskogo A.D.</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>398070</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>https://vinolip.ru</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>221486</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>vinomania48@mail.ru</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="inlineStr"/>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>83671223</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr"/>
+      <c r="S235" s="2" t="inlineStr"/>
+      <c r="T235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr">
+        <is>
+          <t>Ekaterina Vladimirovna Levikova</t>
+        </is>
+      </c>
+      <c r="X235" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y235" s="2" t="inlineStr"/>
+      <c r="Z235" s="2" t="inlineStr"/>
+      <c r="AA235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>VAINVOK, OOO</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Enotop</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>167953</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>St. Petersburg</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>st. Shirokaya, house 18</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>https://enotop.ru</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>104454</t>
+        </is>
+      </c>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>help@enotop.ru</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr"/>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>58832432</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr"/>
+      <c r="S236" s="2" t="inlineStr"/>
+      <c r="T236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr"/>
+      <c r="X236" s="2" t="inlineStr"/>
+      <c r="Y236" s="2" t="inlineStr"/>
+      <c r="Z236" s="2" t="inlineStr"/>
+      <c r="AA236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>OBSHCHESTVO POTREBLENIYA, OOO</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteka Cultura</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>167950</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>St. Petersburg</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>d. 21 str. 1 pom. 3-N, ul. Sotsialisticheskaya</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>191119</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>https://culturawines.ru</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>171140</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>mail@culturawines.ru</t>
+        </is>
+      </c>
+      <c r="O237" s="2" t="inlineStr"/>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>55552293</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr"/>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/culturawines/</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/culturawines</t>
+        </is>
+      </c>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr"/>
+      <c r="W237" s="2" t="inlineStr">
+        <is>
+          <t>Anton Vladimirovich Korotchenko</t>
+        </is>
+      </c>
+      <c r="X237" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr"/>
+      <c r="AA237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>ENOTEKA DOS, OOO</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr"/>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>167949</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Tyumen</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Evropeyskiy microdistrict, Tikhiy proezd, 6</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>https://enoteca72.ru</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>159732</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>enoteka.dos@yandex.ru</t>
+        </is>
+      </c>
+      <c r="O238" s="2" t="inlineStr"/>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>33796103</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr"/>
+      <c r="S238" s="2" t="inlineStr"/>
+      <c r="T238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr"/>
+      <c r="W238" s="2" t="inlineStr">
+        <is>
+          <t>Svetlana Gennadevna Stepanova</t>
+        </is>
+      </c>
+      <c r="X238" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr"/>
+      <c r="AA238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>VINOTEKS, OOO</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr"/>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>167948</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>d. 143 pom. 10, prospekt Komsomolski</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>454103</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>https://bokalleta.ru</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>98276</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>bokalleta174@yandex.ru</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr"/>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>49016716</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr"/>
+      <c r="S239" s="2" t="inlineStr"/>
+      <c r="T239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr">
+        <is>
+          <t>Polina Mikhailovna Lenshina</t>
+        </is>
+      </c>
+      <c r="X239" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y239" s="2" t="inlineStr"/>
+      <c r="Z239" s="2" t="inlineStr"/>
+      <c r="AA239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>0901, OOO</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr"/>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>167947</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Bryansk</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>d. 6A pom. 12, ul. Bezhitskaya</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>241050</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>https://0901wine.ru</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>131451</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>vinoteka0901@mail.ru</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr"/>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>39496945</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr"/>
+      <c r="S240" s="2" t="inlineStr"/>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/0901wine/</t>
+        </is>
+      </c>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr"/>
+      <c r="W240" s="2" t="inlineStr">
+        <is>
+          <t>Shvyrkov Anton Alexandrovich</t>
+        </is>
+      </c>
+      <c r="X240" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="AA240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>LOGINTON, OOO</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr"/>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>167946</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>d. 6 pom. 4N, per. Serebryanicheski</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>109028</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>https://barinwine.ru</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>158422</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>info@barinwine.ru</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr"/>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>51669199</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr"/>
+      <c r="S241" s="2" t="inlineStr"/>
+      <c r="T241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr"/>
+      <c r="W241" s="2" t="inlineStr">
+        <is>
+          <t>Anton Vladimirovich Loginov</t>
+        </is>
+      </c>
+      <c r="X241" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr"/>
+      <c r="AA241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>MARIKO, OOO</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Vinotheque</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>167945</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Stanitsa Taman</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>ul. Krupskoi 14A</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>353556</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>https://vinotheque.ru</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>2550757</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>info@vinotheque.ru</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 444-40-93</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>11393008</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr"/>
+      <c r="S242" s="2" t="inlineStr"/>
+      <c r="T242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotheque.ru/</t>
+        </is>
+      </c>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@vinotheque_ru</t>
+        </is>
+      </c>
+      <c r="W242" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandr Nikolaevich Borkov</t>
+        </is>
+      </c>
+      <c r="X242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General Director </t>
+        </is>
+      </c>
+      <c r="Y242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr"/>
+      <c r="AA242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>VEGA, OOO</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr"/>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>167943</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Kazan</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>zd. 25 pom. 1003, ul. Tovarishcheskaya</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>420097</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>https://hochy116.ru</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>10278645</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>office@hochy116.ru</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr"/>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>46619070</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr"/>
+      <c r="S243" s="2" t="inlineStr"/>
+      <c r="T243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@hochy_116</t>
+        </is>
+      </c>
+      <c r="W243" s="2" t="inlineStr">
+        <is>
+          <t>Ildar Yumadilovich Yarmukhametov</t>
+        </is>
+      </c>
+      <c r="X243" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>STRATEGIYA, OOO</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr"/>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>167941</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Perm</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>d. 12 ofis 35, ul. Torgovaya</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>614101</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>https://dutyfreeperm.ru</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>559681</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>info@dutyfreeprm.ru</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>+7 342 212-92-29</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>88085263</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr"/>
+      <c r="S244" s="2" t="inlineStr"/>
+      <c r="T244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr"/>
+      <c r="W244" s="2" t="inlineStr">
+        <is>
+          <t>Arkadi Andreevich Sysolyatin</t>
+        </is>
+      </c>
+      <c r="X244" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr"/>
+      <c r="AA244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>KREPKI STIL, OOO</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr"/>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>167939</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>d. 12 pom. 1/18, naberezhnaya Krasnopresnenskaya</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>123610</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>https://krepkiystyle.ru</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>857401</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>info@krepkiystyle.ru</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 222-22-85</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>55366343</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr"/>
+      <c r="S245" s="2" t="inlineStr"/>
+      <c r="T245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr"/>
+      <c r="W245" s="2" t="inlineStr">
+        <is>
+          <t>Olesya Viktorovna Shapranova</t>
+        </is>
+      </c>
+      <c r="X245" s="2" t="inlineStr">
+        <is>
+          <t>Director-General</t>
+        </is>
+      </c>
+      <c r="Y245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr"/>
+      <c r="AA245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>WVC JAVA LLC</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr"/>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>167936</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Krasnoyarsk</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>pl. Krasnaya 3B/51</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>660021</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>https://vinotekakrsk.ru</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>725391</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>vinoteka_koktebel@mail.ru</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr"/>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>57695281</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="inlineStr"/>
+      <c r="S246" s="2" t="inlineStr"/>
+      <c r="T246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr"/>
+      <c r="W246" s="2" t="inlineStr">
+        <is>
+          <t>Natalya Viktorovna Silyutina</t>
+        </is>
+      </c>
+      <c r="X246" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="AA246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>LLC VINTAGE</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr"/>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>167935</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>d. 8 kv. 8, ul. Sergiya Radonezhskogo</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>105120</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>https://vintage-vine.ru</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>508382</t>
+        </is>
+      </c>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>info@vintage-vine.ru</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>+7 499 677-21-70</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>46966423</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr"/>
+      <c r="S247" s="2" t="inlineStr"/>
+      <c r="T247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr"/>
+      <c r="W247" s="2" t="inlineStr">
+        <is>
+          <t>Oksana Vladimirovna Khmelnichenko</t>
+        </is>
+      </c>
+      <c r="X247" s="2" t="inlineStr">
+        <is>
+          <t>Director-General</t>
+        </is>
+      </c>
+      <c r="Y247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>CHATEAU MATO LLC</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr"/>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>167934</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Ekaterinburg</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>d. 52 ofisnoe pomeshchenie 33, ul. Aivazovskogo</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>620144</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>https://chatomato.ru</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>chatomato@yandex.ru</t>
+        </is>
+      </c>
+      <c r="O248" s="2" t="inlineStr"/>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>85665787</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="inlineStr"/>
+      <c r="S248" s="2" t="inlineStr"/>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateau_mato/</t>
+        </is>
+      </c>
+      <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="inlineStr"/>
+      <c r="W248" s="2" t="inlineStr">
+        <is>
+          <t>Ekaterina Lvovna Plakhova</t>
+        </is>
+      </c>
+      <c r="X248" s="2" t="inlineStr">
+        <is>
+          <t>Director-General</t>
+        </is>
+      </c>
+      <c r="Y248" s="2" t="inlineStr"/>
+      <c r="Z248" s="2" t="inlineStr"/>
+      <c r="AA248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Auchan</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Auchan</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>49954</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Vavilova St., 3, Office 312</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>119334</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.ru</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr"/>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>pressa@auchan.ru</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-58-00</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="inlineStr"/>
+      <c r="Q249" s="2" t="inlineStr"/>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/auchan-retail/</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr"/>
+      <c r="T249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="inlineStr"/>
+      <c r="W249" s="2" t="inlineStr">
+        <is>
+          <t>Asya Balabay</t>
+        </is>
+      </c>
+      <c r="X249" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y249" s="2" t="inlineStr"/>
+      <c r="Z249" s="2" t="inlineStr"/>
+      <c r="AA249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asyabalabay/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Auchan</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Auchan</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>49954</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Vavilova St., 3, Office 312</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>119334</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.ru</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>pressa@auchan.ru</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-58-00</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="inlineStr"/>
+      <c r="Q250" s="2" t="inlineStr"/>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/auchan-retail/</t>
+        </is>
+      </c>
+      <c r="S250" s="2" t="inlineStr"/>
+      <c r="T250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="2" t="inlineStr"/>
+      <c r="W250" s="2" t="inlineStr">
+        <is>
+          <t>Alexey Zholudev</t>
+        </is>
+      </c>
+      <c r="X250" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Director</t>
+        </is>
+      </c>
+      <c r="Y250" s="2" t="inlineStr"/>
+      <c r="Z250" s="2" t="inlineStr"/>
+      <c r="AA250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexey-zholudev-b6495b11a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Auchan</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Auchan</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>49954</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Vavilova St., 3, Office 312</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>119334</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.ru</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr"/>
+      <c r="M251" s="2" t="inlineStr"/>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>pressa@auchan.ru</t>
+        </is>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-58-00</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="inlineStr"/>
+      <c r="Q251" s="2" t="inlineStr"/>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/auchan-retail/</t>
+        </is>
+      </c>
+      <c r="S251" s="2" t="inlineStr"/>
+      <c r="T251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="inlineStr"/>
+      <c r="W251" s="2" t="inlineStr">
+        <is>
+          <t>Anatoly Fesenko</t>
+        </is>
+      </c>
+      <c r="X251" s="2" t="inlineStr">
+        <is>
+          <t>Regional Head of Procurement and Logistics</t>
+        </is>
+      </c>
+      <c r="Y251" s="2" t="inlineStr"/>
+      <c r="Z251" s="2" t="inlineStr"/>
+      <c r="AA251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%D0%B0%D0%BD%D0%B0%D1%82%D0%BE%D0%BB%D0%B8%D0%B9-%D1%84%D0%B5%D1%81%D0%B5%D0%BD%D0%BA%D0%BE/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Matador, Ooo</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Sabonis</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>105383</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Sankt-Peterburg, Petrogradskiy</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>8 Petrogradskaya naberezhnaya</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>197046</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>https://sabonis.ru</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>info@sabonis.ru</t>
+        </is>
+      </c>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>+7 812 409-96-98</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>87416284</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="inlineStr"/>
+      <c r="S252" s="2" t="inlineStr"/>
+      <c r="T252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="inlineStr"/>
+      <c r="W252" s="2" t="inlineStr"/>
+      <c r="X252" s="2" t="inlineStr"/>
+      <c r="Y252" s="2" t="inlineStr"/>
+      <c r="Z252" s="2" t="inlineStr"/>
+      <c r="AA252" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA252"/>
+  <dimension ref="A1:AA255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25217,6 +25217,297 @@
       <c r="Z252" s="2" t="inlineStr"/>
       <c r="AA252" s="2" t="inlineStr"/>
     </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Vinoterra, Ooo</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Vinoterra, Ooo</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>11672</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>2-nd Zvenigorodskaya, 13 bld 41</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>123033</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoterra.ru</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>referent@vinoterra.ru</t>
+        </is>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 156-16-96</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>96530346</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinoterraru/</t>
+        </is>
+      </c>
+      <c r="S253" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/vinoterra.ru/</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.instagram.com/vinoterra.ru/</t>
+        </is>
+      </c>
+      <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/%D0%92%D0%B8%D0%BD%D0%BE%D1%82%D0%B5%D1%80%D1%80%D0%B0%D0%A2%D0%BE%D1%80%D0%B3%D0%BE%D0%B2%D0%B0%D1%8F%D0%9A%D0%BE%D0%BC%D0%BF%D0%B0%D0%BD%D0%B8%D1%8F/featured</t>
+        </is>
+      </c>
+      <c r="W253" s="2" t="inlineStr">
+        <is>
+          <t>Vlad Volkov</t>
+        </is>
+      </c>
+      <c r="X253" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y253" s="2" t="inlineStr"/>
+      <c r="Z253" s="2" t="inlineStr"/>
+      <c r="AA253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vlad-volkov-22a2801a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Vinoterra, Ooo</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Vinoterra, Ooo</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>11672</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>2-nd Zvenigorodskaya, 13 bld 41</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>123033</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoterra.ru</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>referent@vinoterra.ru</t>
+        </is>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 156-16-96</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>96530346</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinoterraru/</t>
+        </is>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.facebook.com/vinoterra.ru/</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.instagram.com/vinoterra.ru/</t>
+        </is>
+      </c>
+      <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/%D0%92%D0%B8%D0%BD%D0%BE%D1%82%D0%B5%D1%80%D1%80%D0%B0%D0%A2%D0%BE%D1%80%D0%B3%D0%BE%D0%B2%D0%B0%D1%8F%D0%9A%D0%BE%D0%BC%D0%BF%D0%B0%D0%BD%D0%B8%D1%8F/featured</t>
+        </is>
+      </c>
+      <c r="W254" s="2" t="inlineStr">
+        <is>
+          <t>Alexey S.</t>
+        </is>
+      </c>
+      <c r="X254" s="2" t="inlineStr">
+        <is>
+          <t>Wine Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y254" s="2" t="inlineStr"/>
+      <c r="Z254" s="2" t="inlineStr"/>
+      <c r="AA254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexey-s-20341239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Global-alko</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Global-alko</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>96409</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Zamoskvorech'ye</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>House 7, Building 1 Mytnaya Ulitsa</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>119049</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>https://globalalco.ru</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>info@globalalco.ru</t>
+        </is>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 204-91-19</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr"/>
+      <c r="Q255" s="2" t="inlineStr"/>
+      <c r="R255" s="2" t="inlineStr"/>
+      <c r="S255" s="2" t="inlineStr"/>
+      <c r="T255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="inlineStr"/>
+      <c r="W255" s="2" t="inlineStr"/>
+      <c r="X255" s="2" t="inlineStr"/>
+      <c r="Y255" s="2" t="inlineStr"/>
+      <c r="Z255" s="2" t="inlineStr"/>
+      <c r="AA255" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA255"/>
+  <dimension ref="A1:AA260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25508,6 +25508,495 @@
       <c r="Z255" s="2" t="inlineStr"/>
       <c r="AA255" s="2" t="inlineStr"/>
     </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Filevskiy Park</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Novofilevsky Pr., 4/6c2</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>121087</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>https://aroma.ru</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>info@aroma.ru</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 777-55-20</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>44444583</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="inlineStr"/>
+      <c r="S256" s="2" t="inlineStr"/>
+      <c r="T256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="inlineStr"/>
+      <c r="W256" s="2" t="inlineStr"/>
+      <c r="X256" s="2" t="inlineStr"/>
+      <c r="Y256" s="2" t="inlineStr"/>
+      <c r="Z256" s="2" t="inlineStr"/>
+      <c r="AA256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr"/>
+      <c r="M257" s="2" t="inlineStr"/>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S257" s="2" t="inlineStr"/>
+      <c r="T257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W257" s="2" t="inlineStr">
+        <is>
+          <t>Dmitriy Fedorov</t>
+        </is>
+      </c>
+      <c r="X257" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y257" s="2" t="inlineStr"/>
+      <c r="Z257" s="2" t="inlineStr"/>
+      <c r="AA257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dmitriy-fedorov-399671154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr"/>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S258" s="2" t="inlineStr"/>
+      <c r="T258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W258" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Luchkin</t>
+        </is>
+      </c>
+      <c r="X258" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr"/>
+      <c r="AA258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxim-luchkin-b158b24a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr"/>
+      <c r="T259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W259" s="2" t="inlineStr">
+        <is>
+          <t>Svetlana Vdovykh</t>
+        </is>
+      </c>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Specialist/ Operations Director </t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr"/>
+      <c r="Z259" s="2" t="inlineStr"/>
+      <c r="AA259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetlana-vdovykh-28578369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr"/>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S260" s="2" t="inlineStr"/>
+      <c r="T260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W260" s="2" t="inlineStr">
+        <is>
+          <t>Georgy Dzhangirov</t>
+        </is>
+      </c>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr"/>
+      <c r="Z260" s="2" t="inlineStr"/>
+      <c r="AA260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dzhangirov/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA260"/>
+  <dimension ref="A1:AA265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25997,6 +25997,495 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Filevskiy Park</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Novofilevsky Pr., 4/6c2</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>121087</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>https://aroma.ru</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr"/>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>info@aroma.ru</t>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 777-55-20</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>44444583</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr"/>
+      <c r="S261" s="2" t="inlineStr"/>
+      <c r="T261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr"/>
+      <c r="W261" s="2" t="inlineStr"/>
+      <c r="X261" s="2" t="inlineStr"/>
+      <c r="Y261" s="2" t="inlineStr"/>
+      <c r="Z261" s="2" t="inlineStr"/>
+      <c r="AA261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr"/>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S262" s="2" t="inlineStr"/>
+      <c r="T262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W262" s="2" t="inlineStr">
+        <is>
+          <t>Dmitriy Fedorov</t>
+        </is>
+      </c>
+      <c r="X262" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y262" s="2" t="inlineStr"/>
+      <c r="Z262" s="2" t="inlineStr"/>
+      <c r="AA262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dmitriy-fedorov-399671154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr"/>
+      <c r="M263" s="2" t="inlineStr"/>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S263" s="2" t="inlineStr"/>
+      <c r="T263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W263" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Luchkin</t>
+        </is>
+      </c>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr"/>
+      <c r="Z263" s="2" t="inlineStr"/>
+      <c r="AA263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxim-luchkin-b158b24a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S264" s="2" t="inlineStr"/>
+      <c r="T264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W264" s="2" t="inlineStr">
+        <is>
+          <t>Svetlana Vdovykh</t>
+        </is>
+      </c>
+      <c r="X264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Specialist/ Operations Director </t>
+        </is>
+      </c>
+      <c r="Y264" s="2" t="inlineStr"/>
+      <c r="Z264" s="2" t="inlineStr"/>
+      <c r="AA264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetlana-vdovykh-28578369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr"/>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr"/>
+      <c r="T265" s="2" t="inlineStr"/>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W265" s="2" t="inlineStr">
+        <is>
+          <t>Georgy Dzhangirov</t>
+        </is>
+      </c>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr"/>
+      <c r="Z265" s="2" t="inlineStr"/>
+      <c r="AA265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dzhangirov/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA265"/>
+  <dimension ref="A1:AA270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -26486,6 +26486,495 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Filevskiy Park</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Novofilevsky Pr., 4/6c2</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>121087</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>https://aroma.ru</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>info@aroma.ru</t>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 777-55-20</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>44444583</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr"/>
+      <c r="S266" s="2" t="inlineStr"/>
+      <c r="T266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr"/>
+      <c r="W266" s="2" t="inlineStr"/>
+      <c r="X266" s="2" t="inlineStr"/>
+      <c r="Y266" s="2" t="inlineStr"/>
+      <c r="Z266" s="2" t="inlineStr"/>
+      <c r="AA266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr"/>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S267" s="2" t="inlineStr"/>
+      <c r="T267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Luchkin</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxim-luchkin-b158b24a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr"/>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr"/>
+      <c r="T268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t>Dmitriy Fedorov</t>
+        </is>
+      </c>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dmitriy-fedorov-399671154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr"/>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S269" s="2" t="inlineStr"/>
+      <c r="T269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W269" s="2" t="inlineStr">
+        <is>
+          <t>Svetlana Vdovykh</t>
+        </is>
+      </c>
+      <c r="X269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Specialist/ Operations Director </t>
+        </is>
+      </c>
+      <c r="Y269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr"/>
+      <c r="AA269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetlana-vdovykh-28578369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr"/>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr"/>
+      <c r="T270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W270" s="2" t="inlineStr">
+        <is>
+          <t>Georgy Dzhangirov</t>
+        </is>
+      </c>
+      <c r="X270" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr"/>
+      <c r="AA270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dzhangirov/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA270"/>
+  <dimension ref="A1:AA275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -26975,6 +26975,495 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Filevskiy Park</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Novofilevsky Pr., 4/6c2</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>121087</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>https://aroma.ru</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>info@aroma.ru</t>
+        </is>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 777-55-20</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>44444583</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr"/>
+      <c r="S271" s="2" t="inlineStr"/>
+      <c r="T271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr"/>
+      <c r="X271" s="2" t="inlineStr"/>
+      <c r="Y271" s="2" t="inlineStr"/>
+      <c r="Z271" s="2" t="inlineStr"/>
+      <c r="AA271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S272" s="2" t="inlineStr"/>
+      <c r="T272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="inlineStr"/>
+      <c r="V272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W272" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Luchkin</t>
+        </is>
+      </c>
+      <c r="X272" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y272" s="2" t="inlineStr"/>
+      <c r="Z272" s="2" t="inlineStr"/>
+      <c r="AA272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxim-luchkin-b158b24a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S273" s="2" t="inlineStr"/>
+      <c r="T273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W273" s="2" t="inlineStr">
+        <is>
+          <t>Dmitriy Fedorov</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y273" s="2" t="inlineStr"/>
+      <c r="Z273" s="2" t="inlineStr"/>
+      <c r="AA273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dmitriy-fedorov-399671154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr"/>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S274" s="2" t="inlineStr"/>
+      <c r="T274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
+          <t>Svetlana Vdovykh</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Specialist/ Operations Director </t>
+        </is>
+      </c>
+      <c r="Y274" s="2" t="inlineStr"/>
+      <c r="Z274" s="2" t="inlineStr"/>
+      <c r="AA274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetlana-vdovykh-28578369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr"/>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S275" s="2" t="inlineStr"/>
+      <c r="T275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W275" s="2" t="inlineStr">
+        <is>
+          <t>Georgy Dzhangirov</t>
+        </is>
+      </c>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr"/>
+      <c r="Z275" s="2" t="inlineStr"/>
+      <c r="AA275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dzhangirov/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA275"/>
+  <dimension ref="A1:AA280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -27464,6 +27464,495 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Aroma Trading House</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Filevskiy Park</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Novofilevsky Pr., 4/6c2</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>121087</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>https://aroma.ru</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>info@aroma.ru</t>
+        </is>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 777-55-20</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>44444583</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr"/>
+      <c r="S276" s="2" t="inlineStr"/>
+      <c r="T276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr"/>
+      <c r="W276" s="2" t="inlineStr"/>
+      <c r="X276" s="2" t="inlineStr"/>
+      <c r="Y276" s="2" t="inlineStr"/>
+      <c r="Z276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr"/>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S277" s="2" t="inlineStr"/>
+      <c r="T277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W277" s="2" t="inlineStr">
+        <is>
+          <t>Dmitriy Fedorov</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr"/>
+      <c r="AA277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dmitriy-fedorov-399671154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr"/>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr"/>
+      <c r="T278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W278" s="2" t="inlineStr">
+        <is>
+          <t>Maxim Luchkin</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y278" s="2" t="inlineStr"/>
+      <c r="Z278" s="2" t="inlineStr"/>
+      <c r="AA278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxim-luchkin-b158b24a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr"/>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S279" s="2" t="inlineStr"/>
+      <c r="T279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W279" s="2" t="inlineStr">
+        <is>
+          <t>Svetlana Vdovykh</t>
+        </is>
+      </c>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Specialist/ Operations Director </t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetlana-vdovykh-28578369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash And Carry Russia</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>106502</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Moskva</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Levoberezhnyy</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>71 Leningradskoye Highway</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>125445</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr"/>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>shop@metro-cc.ru</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>+7 800 700-10-77</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>54907417</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash-&amp;-carry-russia/</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="inlineStr"/>
+      <c r="T280" s="2" t="inlineStr"/>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroCCru</t>
+        </is>
+      </c>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
+          <t>Georgy Dzhangirov</t>
+        </is>
+      </c>
+      <c r="X280" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y280" s="2" t="inlineStr"/>
+      <c r="Z280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dzhangirov/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
